--- a/SGC-CKN/Excel/eec28b76-003b-42df-b6d0-ec697b48b325_P2_P2-7_D800_07-04-2026.xlsx
+++ b/SGC-CKN/Excel/eec28b76-003b-42df-b6d0-ec697b48b325_P2_P2-7_D800_07-04-2026.xlsx
@@ -98,7 +98,7 @@
     <t>Đất thổ nhưỡng</t>
   </si>
   <si>
-    <t xml:space="preserve">12:40
+    <t xml:space="preserve">17:40
 06/04/2026</t>
   </si>
   <si>
@@ -219,7 +219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -250,18 +250,12 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF78350F"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -308,7 +302,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,7 +331,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -347,7 +341,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -368,11 +362,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9F99D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -478,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -513,47 +502,53 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -564,22 +559,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1168,16 +1154,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-3.8</v>
+        <v>-2.8</v>
       </c>
       <c r="H11" s="5">
-        <v>5.25</v>
+        <v>0.25</v>
       </c>
       <c r="I11" s="5">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J11" s="8">
-        <v>0.72</v>
+        <v>11.2</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1200,19 +1186,19 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-3.8</v>
+        <v>-2.8</v>
       </c>
       <c r="G12" s="9">
-        <v>-7.6</v>
+        <v>-3.6</v>
       </c>
       <c r="H12" s="9">
         <v>0.25</v>
       </c>
       <c r="I12" s="9">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J12" s="12">
-        <v>15.2</v>
+        <v>3.2</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1235,7 +1221,7 @@
         <v>36</v>
       </c>
       <c r="F13" s="13">
-        <v>-7.6</v>
+        <v>-3.6</v>
       </c>
       <c r="G13" s="13">
         <v>-8.7</v>
@@ -1244,10 +1230,10 @@
         <v>0.17</v>
       </c>
       <c r="I13" s="13">
-        <v>1.1</v>
-      </c>
-      <c r="J13" s="12">
-        <v>6.6</v>
+        <v>5.1</v>
+      </c>
+      <c r="J13" s="8">
+        <v>30.6</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1281,7 +1267,7 @@
       <c r="I14" s="16">
         <v>3.3</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="8">
         <v>11.65</v>
       </c>
       <c r="K14" s="17" t="s">
@@ -1316,7 +1302,7 @@
       <c r="I15" s="19">
         <v>12</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="8">
         <v>9.86</v>
       </c>
       <c r="K15" s="20" t="s">
@@ -1351,7 +1337,7 @@
       <c r="I16" s="22">
         <v>5</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="12">
         <v>5</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -1359,89 +1345,89 @@
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="25">
         <v>-29</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <v>-39.5</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <v>1.67</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="25">
         <v>10.5</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="8">
         <v>6.3</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="26" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <v>-39.5</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>-44.5</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>3.12</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="28">
         <v>5</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="12">
         <v>1.6</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="29" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1580,16 +1566,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-3.8</v>
+        <v>-2.8</v>
       </c>
       <c r="G2" s="5">
-        <v>5.25</v>
+        <v>0.25</v>
       </c>
       <c r="H2" s="5">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="I2" s="8">
-        <v>0.72</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1606,19 +1592,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-3.8</v>
+        <v>-2.8</v>
       </c>
       <c r="F3" s="9">
-        <v>-7.6</v>
+        <v>-3.6</v>
       </c>
       <c r="G3" s="9">
         <v>0.25</v>
       </c>
       <c r="H3" s="9">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="I3" s="12">
-        <v>15.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1635,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>-7.6</v>
+        <v>-3.6</v>
       </c>
       <c r="F4" s="13">
         <v>-8.7</v>
@@ -1644,10 +1630,10 @@
         <v>0.17</v>
       </c>
       <c r="H4" s="13">
-        <v>1.1</v>
-      </c>
-      <c r="I4" s="12">
-        <v>6.6</v>
+        <v>5.1</v>
+      </c>
+      <c r="I4" s="8">
+        <v>30.6</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1675,7 +1661,7 @@
       <c r="H5" s="16">
         <v>3.3</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="8">
         <v>11.65</v>
       </c>
     </row>
@@ -1704,7 +1690,7 @@
       <c r="H6" s="19">
         <v>12</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="8">
         <v>9.86</v>
       </c>
     </row>
@@ -1733,95 +1719,95 @@
       <c r="H7" s="22">
         <v>5</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>-29</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="25">
         <v>-39.5</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="25">
         <v>1.67</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <v>10.5</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="8">
         <v>6.3</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>-39.5</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>-44.5</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>3.12</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>5</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="12">
         <v>1.6</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>0</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <v>-44.5</v>
       </c>
-      <c r="G10" s="34">
-        <v>12.95</v>
-      </c>
-      <c r="H10" s="34">
+      <c r="G10" s="33">
+        <v>7.95</v>
+      </c>
+      <c r="H10" s="33">
         <v>44.5</v>
       </c>
-      <c r="I10" s="34">
-        <v>3.44</v>
+      <c r="I10" s="33">
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
